--- a/etf_holdings/2026-10-06_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:11</t>
+          <t>2026-10-06 01:25:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:11</t>
+          <t>2026-10-06 01:25:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:11</t>
+          <t>2026-10-06 01:25:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:11</t>
+          <t>2026-10-06 01:25:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:11</t>
+          <t>2026-10-06 01:25:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:11</t>
+          <t>2026-10-06 01:25:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:11</t>
+          <t>2026-10-06 01:25:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:11</t>
+          <t>2026-10-06 01:25:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:11</t>
+          <t>2026-10-06 01:25:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:11</t>
+          <t>2026-10-06 01:25:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:11</t>
+          <t>2026-10-06 01:25:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:11</t>
+          <t>2026-10-06 01:25:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:11</t>
+          <t>2026-10-06 01:25:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:11</t>
+          <t>2026-10-06 01:25:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:11</t>
+          <t>2026-10-06 01:25:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:12</t>
+          <t>2026-10-06 01:25:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:12</t>
+          <t>2026-10-06 01:25:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:12</t>
+          <t>2026-10-06 01:25:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:12</t>
+          <t>2026-10-06 01:25:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:12</t>
+          <t>2026-10-06 01:25:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:12</t>
+          <t>2026-10-06 01:25:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:12</t>
+          <t>2026-10-06 01:25:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:12</t>
+          <t>2026-10-06 01:25:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:12</t>
+          <t>2026-10-06 01:25:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:12</t>
+          <t>2026-10-06 01:25:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:12</t>
+          <t>2026-10-06 01:25:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:12</t>
+          <t>2026-10-06 01:25:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:12</t>
+          <t>2026-10-06 01:25:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:12</t>
+          <t>2026-10-06 01:25:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:12</t>
+          <t>2026-10-06 01:25:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:13</t>
+          <t>2026-10-06 01:25:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:13</t>
+          <t>2026-10-06 01:25:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:13</t>
+          <t>2026-10-06 01:25:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:13</t>
+          <t>2026-10-06 01:25:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:13</t>
+          <t>2026-10-06 01:25:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:13</t>
+          <t>2026-10-06 01:25:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:13</t>
+          <t>2026-10-06 01:25:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:13</t>
+          <t>2026-10-06 01:25:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:13</t>
+          <t>2026-10-06 01:25:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:13</t>
+          <t>2026-10-06 01:25:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:13</t>
+          <t>2026-10-06 01:25:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:13</t>
+          <t>2026-10-06 01:25:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:13</t>
+          <t>2026-10-06 01:25:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:13</t>
+          <t>2026-10-06 01:25:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:17:13</t>
+          <t>2026-10-06 01:25:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-10-06_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:15</t>
+          <t>2026-10-06 02:28:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:16</t>
+          <t>2026-10-06 02:28:47</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:18</t>
+          <t>2026-10-06 02:28:48</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-10-06_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:45</t>
+          <t>2026-10-06 19:17:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+3%2575</t>
+          <t>+0.39%2585</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2575</v>
+        <v>2585</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.67%1,034,000</t>
+          <t>8.63%1,034,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.67%</t>
+          <t>8.63%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:45</t>
+          <t>2026-10-06 19:17:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+4.34%5165</t>
+          <t>-4.74%4920</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+4.34%</t>
+          <t>-4.74%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5165</v>
+        <v>4920</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.95%413,000</t>
+          <t>6.56%413,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>6.56%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:45</t>
+          <t>2026-10-06 19:17:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+9.96%13355</t>
+          <t>+5.18%5995</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>+5.18%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>13355</v>
+        <v>5995</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.35%123,000</t>
+          <t>5.46%282,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.35%</t>
+          <t>5.46%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>123000</v>
+        <v>282000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:45</t>
+          <t>2026-10-06 19:17:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+9.93%5700</t>
+          <t>-1.91%13100</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5700</v>
+        <v>13100</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.23%282,000</t>
+          <t>5.20%123,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>5.20%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>282000</v>
+        <v>123000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:45</t>
+          <t>2026-10-06 19:17:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+1.53%1325</t>
+          <t>-1.13%1310</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1325</v>
+        <v>1310</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.22%1,209,000</t>
+          <t>5.11%1,209,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.22%</t>
+          <t>5.11%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:45</t>
+          <t>2026-10-06 19:17:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+5.96%7205</t>
+          <t>-1.73%7080</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+5.96%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7205</v>
+        <v>7080</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.18%221,000</t>
+          <t>5.05%221,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.18%</t>
+          <t>5.05%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:45</t>
+          <t>2026-10-06 19:17:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+4.22%3585</t>
+          <t>+2.79%3685</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+4.22%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3585</v>
+        <v>3685</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.40%377,000</t>
+          <t>4.49%377,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.40%</t>
+          <t>4.49%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:45</t>
+          <t>2026-10-06 19:17:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+6.37%2005</t>
+          <t>+2.24%2050</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+6.37%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2005</v>
+        <v>2050</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.37%669,000</t>
+          <t>4.43%669,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.37%</t>
+          <t>4.43%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:45</t>
+          <t>2026-10-06 19:17:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+8.86%8600</t>
+          <t>-2.62%8375</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+8.86%</t>
+          <t>-2.62%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>8600</v>
+        <v>8375</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.34%155,000</t>
+          <t>4.19%155,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>4.19%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:45</t>
+          <t>2026-10-06 19:17:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+10%286</t>
+          <t>+2.45%293</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+2.45%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.88%4,167,000</t>
+          <t>3.94%4,167,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>3.94%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:45</t>
+          <t>2026-10-06 19:17:52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+6.16%2325</t>
+          <t>+1.08%2350</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2325</v>
+        <v>2350</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.56%470,000</t>
+          <t>3.57%470,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:45</t>
+          <t>2026-10-06 19:17:52</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.84%1180</t>
+          <t>+2.12%1205</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1180</v>
+        <v>1205</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.40%884,000</t>
+          <t>3.44%884,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:45</t>
+          <t>2026-10-06 19:17:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+3.95%5520</t>
+          <t>+2.72%5670</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5520</v>
+        <v>5670</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.25%181,000</t>
+          <t>3.31%181,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.31%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:45</t>
+          <t>2026-10-06 19:17:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+3.12%2150</t>
+          <t>+6.51%2290</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+3.12%</t>
+          <t>+6.51%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2150</v>
+        <v>2290</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.07%438,197</t>
+          <t>3.24%438,197</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:45</t>
+          <t>2026-10-06 19:17:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+3.61%19520</t>
+          <t>+3.02%1535</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+3.61%</t>
+          <t>+3.02%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>19520</v>
+        <v>1535</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.01%47,400</t>
+          <t>2.95%596,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>2.95%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>47400</v>
+        <v>596000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:47</t>
+          <t>2026-10-06 19:17:53</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+9.96%1490</t>
+          <t>-2.74%18985</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1490</v>
+        <v>18985</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.89%596,000</t>
+          <t>2.91%47,400</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.91%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>596000</v>
+        <v>47400</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:47</t>
+          <t>2026-10-06 19:17:53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.17%2485</t>
+          <t>-6.44%2325</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.17%</t>
+          <t>-6.44%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2485</v>
+        <v>2325</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.39%295,000</t>
+          <t>2.21%295,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:47</t>
+          <t>2026-10-06 19:17:53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.4%98.6</t>
+          <t>+2.94%101.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+2.94%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>98.59999999999999</v>
+        <v>101.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.97%6,147,000</t>
+          <t>2.01%6,147,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:47</t>
+          <t>2026-10-06 19:17:53</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+2.77%557</t>
+          <t>+3.95%579</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+2.77%</t>
+          <t>+3.95%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>557</v>
+        <v>579</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.88%1,034,000</t>
+          <t>1.93%1,034,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:47</t>
+          <t>2026-10-06 19:17:53</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+1%152</t>
+          <t>+1.64%154.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>152</v>
+        <v>154.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.54%3,104,000</t>
+          <t>1.55%3,104,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:47</t>
+          <t>2026-10-06 19:17:53</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0%213.5</t>
+          <t>+3.7%1260</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>213.5</v>
+        <v>1260</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.53%2,208,000</t>
+          <t>1.54%378,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>2208000</v>
+        <v>378000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:47</t>
+          <t>2026-10-06 19:17:53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+9.95%1215</t>
+          <t>+0.7%215</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+9.95%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1215</v>
+        <v>215</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.50%378,000</t>
+          <t>1.53%2,208,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>378000</v>
+        <v>2208000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:47</t>
+          <t>2026-10-06 19:17:53</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.47%3155</t>
+          <t>-1.27%3115</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3155</v>
+        <v>3115</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.36%132,000</t>
+          <t>1.33%132,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:47</t>
+          <t>2026-10-06 19:17:53</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+4.07%742</t>
+          <t>+0.27%744</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+4.07%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.12%464,000</t>
+          <t>1.11%464,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:47</t>
+          <t>2026-10-06 19:17:53</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-5.57%152.5</t>
+          <t>-3.28%147.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.57%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>152.5</v>
+        <v>147.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.04%2,096,000</t>
+          <t>1.00%2,096,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:47</t>
+          <t>2026-10-06 19:17:53</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.51%294</t>
+          <t>+1.36%298</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:47</t>
+          <t>2026-10-06 19:17:53</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+9.96%248.5</t>
+          <t>+1.41%252</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>248.5</v>
+        <v>252</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:47</t>
+          <t>2026-10-06 19:17:53</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.29%234.5</t>
+          <t>+0.85%236.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.29%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>234.5</v>
+        <v>236.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:47</t>
+          <t>2026-10-06 19:17:53</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+7%6730</t>
+          <t>+1.86%6855</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6730</v>
+        <v>6855</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.85%39,000</t>
+          <t>0.86%39,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:47</t>
+          <t>2026-10-06 19:17:53</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7750新代</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+9.81%2070</t>
+          <t>+0.79%256</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+9.81%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2070</v>
+        <v>256</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.82%122,000</t>
+          <t>0.79%960,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>122000</v>
+        <v>960000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:48</t>
+          <t>2026-10-06 19:17:55</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>7750新代</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+2.56%3000</t>
+          <t>-4.35%1980</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>-4.35%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3000</v>
+        <v>1980</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.80%82,000</t>
+          <t>0.78%122,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>82000</v>
+        <v>122000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:48</t>
+          <t>2026-10-06 19:17:55</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.2%254</t>
+          <t>-2.67%2920</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>-2.67%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>254</v>
+        <v>2920</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.79%960,000</t>
+          <t>0.77%82,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>960000</v>
+        <v>82000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:48</t>
+          <t>2026-10-06 19:17:55</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+6.63%498.5</t>
+          <t>-2.21%487.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+6.63%</t>
+          <t>-2.21%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>498.5</v>
+        <v>487.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.55%340,000</t>
+          <t>0.54%340,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:48</t>
+          <t>2026-10-06 19:17:55</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.38%220</t>
+          <t>+6.36%234</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>+6.36%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.48%669,000</t>
+          <t>0.51%669,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:48</t>
+          <t>2026-10-06 19:17:55</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3533嘉澤</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.08%1875</t>
+          <t>+5.82%4180</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+5.82%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1875</v>
+        <v>4180</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.47%77,000</t>
+          <t>0.49%36,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>77000</v>
+        <v>36000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:48</t>
+          <t>2026-10-06 19:17:55</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>3533嘉澤</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+3.67%3950</t>
+          <t>-0.53%1865</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+3.67%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3950</v>
+        <v>1865</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.46%36,000</t>
+          <t>0.46%77,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>36000</v>
+        <v>77000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:48</t>
+          <t>2026-10-06 19:17:55</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+6.35%620</t>
+          <t>-0.16%619</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+6.35%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:48</t>
+          <t>2026-10-06 19:17:55</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1.53%996</t>
+          <t>+2.41%1020</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+2.41%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>996</v>
+        <v>1020</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.37%115,000</t>
+          <t>0.38%115,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:48</t>
+          <t>2026-10-06 19:17:55</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.38%794</t>
+          <t>-1.76%780</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.34%133,000</t>
+          <t>0.33%133,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:48</t>
+          <t>2026-10-06 19:17:55</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.29%173</t>
+          <t>0%173</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:48</t>
+          <t>2026-10-06 19:17:55</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.11%97.7</t>
+          <t>+2.35%100</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>+2.35%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:48</t>
+          <t>2026-10-06 19:17:55</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+1.71%238.5</t>
+          <t>0%238.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+1.71%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:48</t>
+          <t>2026-10-06 19:17:55</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.26%382</t>
+          <t>-2.49%372.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>382</v>
+        <v>372.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.22%178,000</t>
+          <t>0.21%178,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:48</t>
+          <t>2026-10-06 19:17:55</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+4.21%5815</t>
+          <t>+1.55%5905</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+4.21%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5815</v>
+        <v>5905</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:48</t>
+          <t>2026-10-06 19:17:55</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+1.61%126.5</t>
+          <t>0%126.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+1.61%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H46" t="n">

--- a/etf_holdings/2026-10-06_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:52</t>
+          <t>2026-10-06 23:21:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:52</t>
+          <t>2026-10-06 23:21:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:52</t>
+          <t>2026-10-06 23:21:14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:52</t>
+          <t>2026-10-06 23:21:14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:52</t>
+          <t>2026-10-06 23:21:14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:52</t>
+          <t>2026-10-06 23:21:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:52</t>
+          <t>2026-10-06 23:21:14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:52</t>
+          <t>2026-10-06 23:21:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:52</t>
+          <t>2026-10-06 23:21:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:52</t>
+          <t>2026-10-06 23:21:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:52</t>
+          <t>2026-10-06 23:21:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:52</t>
+          <t>2026-10-06 23:21:14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:52</t>
+          <t>2026-10-06 23:21:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:52</t>
+          <t>2026-10-06 23:21:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:52</t>
+          <t>2026-10-06 23:21:14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:53</t>
+          <t>2026-10-06 23:21:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:53</t>
+          <t>2026-10-06 23:21:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:53</t>
+          <t>2026-10-06 23:21:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:53</t>
+          <t>2026-10-06 23:21:15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:53</t>
+          <t>2026-10-06 23:21:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:53</t>
+          <t>2026-10-06 23:21:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:53</t>
+          <t>2026-10-06 23:21:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:53</t>
+          <t>2026-10-06 23:21:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:53</t>
+          <t>2026-10-06 23:21:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:53</t>
+          <t>2026-10-06 23:21:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:53</t>
+          <t>2026-10-06 23:21:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:53</t>
+          <t>2026-10-06 23:21:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:53</t>
+          <t>2026-10-06 23:21:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:53</t>
+          <t>2026-10-06 23:21:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:53</t>
+          <t>2026-10-06 23:21:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:55</t>
+          <t>2026-10-06 23:21:16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:55</t>
+          <t>2026-10-06 23:21:16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:55</t>
+          <t>2026-10-06 23:21:16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:55</t>
+          <t>2026-10-06 23:21:16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:55</t>
+          <t>2026-10-06 23:21:16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:55</t>
+          <t>2026-10-06 23:21:16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:55</t>
+          <t>2026-10-06 23:21:16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:55</t>
+          <t>2026-10-06 23:21:16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:55</t>
+          <t>2026-10-06 23:21:16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:55</t>
+          <t>2026-10-06 23:21:16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:55</t>
+          <t>2026-10-06 23:21:16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:55</t>
+          <t>2026-10-06 23:21:16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:55</t>
+          <t>2026-10-06 23:21:16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:55</t>
+          <t>2026-10-06 23:21:16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:55</t>
+          <t>2026-10-06 23:21:16</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-10-06_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:14</t>
+          <t>2026-10-06 23:28:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:14</t>
+          <t>2026-10-06 23:28:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:14</t>
+          <t>2026-10-06 23:28:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:14</t>
+          <t>2026-10-06 23:28:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:14</t>
+          <t>2026-10-06 23:28:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:14</t>
+          <t>2026-10-06 23:28:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:14</t>
+          <t>2026-10-06 23:28:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:14</t>
+          <t>2026-10-06 23:28:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:14</t>
+          <t>2026-10-06 23:28:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:14</t>
+          <t>2026-10-06 23:28:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:14</t>
+          <t>2026-10-06 23:28:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:14</t>
+          <t>2026-10-06 23:28:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:14</t>
+          <t>2026-10-06 23:28:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:14</t>
+          <t>2026-10-06 23:28:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:14</t>
+          <t>2026-10-06 23:28:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:15</t>
+          <t>2026-10-06 23:28:58</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:15</t>
+          <t>2026-10-06 23:28:58</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:15</t>
+          <t>2026-10-06 23:28:58</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:15</t>
+          <t>2026-10-06 23:28:58</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:15</t>
+          <t>2026-10-06 23:28:58</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:15</t>
+          <t>2026-10-06 23:28:58</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:15</t>
+          <t>2026-10-06 23:28:58</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:15</t>
+          <t>2026-10-06 23:28:58</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:15</t>
+          <t>2026-10-06 23:28:58</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:15</t>
+          <t>2026-10-06 23:28:58</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:15</t>
+          <t>2026-10-06 23:28:58</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:15</t>
+          <t>2026-10-06 23:28:58</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:15</t>
+          <t>2026-10-06 23:28:58</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:15</t>
+          <t>2026-10-06 23:28:58</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:15</t>
+          <t>2026-10-06 23:28:58</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:16</t>
+          <t>2026-10-06 23:28:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:16</t>
+          <t>2026-10-06 23:28:59</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:16</t>
+          <t>2026-10-06 23:28:59</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:16</t>
+          <t>2026-10-06 23:28:59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:16</t>
+          <t>2026-10-06 23:28:59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:16</t>
+          <t>2026-10-06 23:28:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:16</t>
+          <t>2026-10-06 23:28:59</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:16</t>
+          <t>2026-10-06 23:28:59</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:16</t>
+          <t>2026-10-06 23:28:59</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:16</t>
+          <t>2026-10-06 23:28:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:16</t>
+          <t>2026-10-06 23:28:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:16</t>
+          <t>2026-10-06 23:28:59</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:16</t>
+          <t>2026-10-06 23:28:59</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:16</t>
+          <t>2026-10-06 23:28:59</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:21:16</t>
+          <t>2026-10-06 23:28:59</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-10-06_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:57</t>
+          <t>2026-10-06 23:59:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:58</t>
+          <t>2026-10-06 23:59:35</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:59</t>
+          <t>2026-10-06 23:59:36</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
